--- a/artfynd/A 41923-2026 artfynd.xlsx
+++ b/artfynd/A 41923-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128291332</v>
+        <v>137520766</v>
       </c>
       <c r="B2" t="n">
-        <v>57950</v>
+        <v>79202</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kallåsen, Dlr</t>
+          <t>Tallåsen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496511</v>
+        <v>496550</v>
       </c>
       <c r="R2" t="n">
-        <v>6774380</v>
+        <v>6774539</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +745,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Silverstubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,65 +780,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128291332</t>
+          <t>https://artportalen.se/Sighting/137520766</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128291333</v>
+        <v>137520763</v>
       </c>
       <c r="B3" t="n">
-        <v>57950</v>
+        <v>79536</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kallåsen, Dlr</t>
+          <t>Tallåsen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496585</v>
+        <v>496584</v>
       </c>
       <c r="R3" t="n">
-        <v>6774537</v>
+        <v>6774650</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +862,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gammal tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,27 +897,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128291333</t>
+          <t>https://artportalen.se/Sighting/137520763</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128291322</v>
+        <v>137520673</v>
       </c>
       <c r="B4" t="n">
-        <v>57953</v>
+        <v>80155</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,45 +925,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kallåsen, Dlr</t>
+          <t>Tallåsen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496530</v>
+        <v>496521</v>
       </c>
       <c r="R4" t="n">
-        <v>6774395</v>
+        <v>6774345</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,27 +979,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>högt upp i tall</t>
+          <t>Silverstubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,27 +1014,27 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128291322</t>
+          <t>https://artportalen.se/Sighting/137520673</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128291339</v>
+        <v>128291332</v>
       </c>
       <c r="B5" t="n">
-        <v>8455</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1064,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496650</v>
+        <v>496511</v>
       </c>
       <c r="R5" t="n">
-        <v>6774498</v>
+        <v>6774380</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,6 +1136,472 @@
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128291332</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128291333</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>496585</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6774537</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128291333</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137520768</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58032</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>496568</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6774447</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137520768</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128291322</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>496530</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6774395</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>högt upp i tall</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128291322</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128291339</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>496650</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6774498</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128291339</t>
         </is>
@@ -1145,6 +1613,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41923-2026 artfynd.xlsx
+++ b/artfynd/A 41923-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137520766</v>
       </c>
       <c r="B2" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,45 +797,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137520763</v>
+        <v>137569196</v>
       </c>
       <c r="B3" t="n">
-        <v>79536</v>
+        <v>92189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tallåsen, Dlr</t>
+          <t>KALLÅSEN, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496584</v>
+        <v>496518</v>
       </c>
       <c r="R3" t="n">
-        <v>6774650</v>
+        <v>6774358</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -867,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +880,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gammal tall</t>
+          <t>Imponerande mycket på knäckt gran. Runt hela stubben och resupinat på undersidan av den liggande stammen.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,33 +894,34 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137520763</t>
+          <t>https://artportalen.se/Sighting/137569196</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137520673</v>
+        <v>137569188</v>
       </c>
       <c r="B4" t="n">
-        <v>80155</v>
+        <v>92210</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,34 +929,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tallåsen, Dlr</t>
+          <t>KALLÅSEN, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496521</v>
+        <v>496580</v>
       </c>
       <c r="R4" t="n">
-        <v>6774345</v>
+        <v>6774554</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -984,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:46</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Silverstubbe</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,65 +1013,65 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137520673</t>
+          <t>https://artportalen.se/Sighting/137569188</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128291332</v>
+        <v>137520763</v>
       </c>
       <c r="B5" t="n">
-        <v>57950</v>
+        <v>79539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kallåsen, Dlr</t>
+          <t>Tallåsen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496511</v>
+        <v>496584</v>
       </c>
       <c r="R5" t="n">
-        <v>6774380</v>
+        <v>6774650</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,22 +1095,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På gammal tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,49 +1130,49 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128291332</t>
+          <t>https://artportalen.se/Sighting/137520763</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128291333</v>
+        <v>137522648</v>
       </c>
       <c r="B6" t="n">
-        <v>57950</v>
+        <v>79539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1178,13 +1182,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496585</v>
+        <v>496593</v>
       </c>
       <c r="R6" t="n">
-        <v>6774537</v>
+        <v>6774647</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,22 +1212,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,62 +1242,62 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Håkan Thenander, Peter Turander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128291333</t>
+          <t>https://artportalen.se/Sighting/137522648</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137520768</v>
+        <v>137522650</v>
       </c>
       <c r="B7" t="n">
-        <v>58032</v>
+        <v>79539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tallåsen, Dlr</t>
+          <t>Kallåsen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496568</v>
+        <v>496588</v>
       </c>
       <c r="R7" t="n">
-        <v>6774447</v>
+        <v>6774621</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1325,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,12 +1339,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,73 +1354,65 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Håkan Thenander, Peter Turander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137520768</t>
+          <t>https://artportalen.se/Sighting/137522650</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128291322</v>
+        <v>137522655</v>
       </c>
       <c r="B8" t="n">
-        <v>57953</v>
+        <v>79539</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kallåsen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496530</v>
+        <v>496587</v>
       </c>
       <c r="R8" t="n">
-        <v>6774395</v>
+        <v>6774536</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1445,27 +1436,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>högt upp i tall</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1480,49 +1466,49 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Håkan Thenander, Peter Turander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128291322</t>
+          <t>https://artportalen.se/Sighting/137522655</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128291339</v>
+        <v>137522658</v>
       </c>
       <c r="B9" t="n">
-        <v>8455</v>
+        <v>79539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1532,13 +1518,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496650</v>
+        <v>496532</v>
       </c>
       <c r="R9" t="n">
-        <v>6774498</v>
+        <v>6774431</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1562,22 +1548,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1592,18 +1578,1985 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Håkan Thenander, Peter Turander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137522658</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137522733</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79539</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>496583</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6774387</v>
+      </c>
+      <c r="S10" t="n">
+        <v>6</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137522733</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137522734</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79539</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>496595</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6774546</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137522734</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137523378</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79539</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kallåsen Gräftmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>496606</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6774647</v>
+      </c>
+      <c r="S12" t="n">
+        <v>6</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Tämligen rikligt på en tall</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Peter Turander, Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137523378</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137569191</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79539</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>KALLÅSEN, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>496615</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6774458</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137569191</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137569199</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79539</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>KALLÅSEN, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>496518</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6774358</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137569199</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137520673</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80158</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Tallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>496521</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6774345</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Silverstubbe</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137520673</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128291332</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>496511</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6774380</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128291332</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128291333</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>496585</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6774537</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128291333</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137520768</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Tallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>496568</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6774447</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137520768</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137523379</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kallåsen Gräftmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>496601</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6774553</v>
+      </c>
+      <c r="S19" t="n">
+        <v>14</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska spår i död gran</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Peter Turander, Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137523379</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137569190</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>KALLÅSEN, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>496584</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6774541</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>I högstubbe, knäck gran</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137569190</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137569198</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>KALLÅSEN, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>496518</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6774358</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137569198</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128291322</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>496530</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6774395</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>högt upp i tall</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128291322</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137569335</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57224</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>KALLÅSEN, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>496568</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6774384</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>osäker</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137569335</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128291339</v>
+      </c>
+      <c r="B24" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>496650</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6774498</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/128291339</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137522656</v>
+      </c>
+      <c r="B25" t="n">
+        <v>8470</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>496587</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6774536</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137522656</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>137569200</v>
+      </c>
+      <c r="B26" t="n">
+        <v>111438</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>KALLÅSEN, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>496513</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6774368</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137569200</t>
         </is>
       </c>
     </row>
@@ -1617,6 +3570,23 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
